--- a/_documentation/Costs.xlsx
+++ b/_documentation/Costs.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Nano Banana (Gemini 2.5 Flash Image)</t>
   </si>
@@ -76,15 +76,34 @@
   </si>
   <si>
     <t>x-ai/grok-imagine-video</t>
+  </si>
+  <si>
+    <t>Veo 3.1 Fast</t>
+  </si>
+  <si>
+    <t>With Audio</t>
+  </si>
+  <si>
+    <t>w/o Audio</t>
+  </si>
+  <si>
+    <t>w Audio</t>
+  </si>
+  <si>
+    <t>Gemini 2.5 Flash</t>
+  </si>
+  <si>
+    <t>Gemini 3.1 Flash Image</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00000_);[Red]\(&quot;$&quot;#,##0.00000\)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -135,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -169,6 +188,12 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -450,19 +475,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
     <col min="3" max="3" width="35.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="11" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
@@ -471,31 +497,35 @@
         <v>8</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="11"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>ROW()-2</f>
         <v>1</v>
@@ -506,14 +536,14 @@
       <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="13">
         <v>1.43E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f>ROW()-2</f>
         <v>2</v>
@@ -524,14 +554,14 @@
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="13">
         <v>3.9300000000000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f>ROW()-2</f>
         <v>3</v>
@@ -539,59 +569,47 @@
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <f t="shared" ref="A6:A8" si="0">ROW()-2</f>
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2.52</v>
-      </c>
-      <c r="F6" s="9">
-        <v>15</v>
-      </c>
-      <c r="G6" s="2">
-        <f>E6/F6</f>
-        <v>0.16800000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="13">
+        <v>1.09E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="13">
+        <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A7:A9" si="0">ROW()-2</f>
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2.4</v>
-      </c>
-      <c r="F7" s="9">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="13">
+        <v>2.52</v>
+      </c>
+      <c r="G7" s="9">
         <v>15</v>
       </c>
-      <c r="G7" s="2">
-        <f t="shared" ref="G7:G8" si="1">E7/F7</f>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H7" s="2">
+        <f>F7/G7</f>
+        <v>0.16800000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -600,30 +618,76 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="13">
+        <v>3.2</v>
+      </c>
+      <c r="G8" s="9">
+        <v>8</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" ref="H8:H10" si="1">F8/G8</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F9" s="13">
         <v>0.752</v>
       </c>
-      <c r="F8" s="9">
+      <c r="G9" s="9">
         <v>15</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H9" s="2">
         <f t="shared" si="1"/>
         <v>5.0133333333333335E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E11" s="2"/>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0.64</v>
+      </c>
+      <c r="G10" s="9">
+        <v>8</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
